--- a/outputs/week2_excel/688758_赛分科技_三表抽取.xlsx
+++ b/outputs/week2_excel/688758_赛分科技_三表抽取.xlsx
@@ -2876,7 +2876,7 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>张松满</t>
+          <t>孙国敏</t>
         </is>
       </c>
       <c r="E34" t="inlineStr"/>
@@ -2894,7 +2894,11 @@
           <t>PASS</t>
         </is>
       </c>
-      <c r="L34" t="inlineStr"/>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>退出</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -2914,7 +2918,7 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>孙国敏</t>
+          <t>张松满</t>
         </is>
       </c>
       <c r="E35" t="inlineStr"/>
@@ -2932,11 +2936,7 @@
           <t>PASS</t>
         </is>
       </c>
-      <c r="L35" t="inlineStr">
-        <is>
-          <t>退出</t>
-        </is>
-      </c>
+      <c r="L35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -2956,7 +2956,7 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>东方富海（上海）创业投资企业（有限合伙）</t>
+          <t>芜湖富海浩研创业投资基金（有限合伙）</t>
         </is>
       </c>
       <c r="E36" t="inlineStr"/>
@@ -3036,15 +3036,11 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>深圳市云汉电子有限公司</t>
+          <t>东方富海（上海）创业投资企业（有限合伙）</t>
         </is>
       </c>
       <c r="E38" t="inlineStr"/>
-      <c r="F38" t="inlineStr">
-        <is>
-          <t>25.0</t>
-        </is>
-      </c>
+      <c r="F38" t="inlineStr"/>
       <c r="G38" t="inlineStr"/>
       <c r="H38" t="inlineStr"/>
       <c r="I38" t="inlineStr"/>
@@ -3056,7 +3052,7 @@
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -3116,11 +3112,15 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>芜湖富海浩研创业投资基金（有限合伙）</t>
+          <t>深圳市云汉电子有限公司</t>
         </is>
       </c>
       <c r="E40" t="inlineStr"/>
-      <c r="F40" t="inlineStr"/>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>25.0</t>
+        </is>
+      </c>
       <c r="G40" t="inlineStr"/>
       <c r="H40" t="inlineStr"/>
       <c r="I40" t="inlineStr"/>
@@ -3132,7 +3132,7 @@
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -3154,7 +3154,7 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>东方富海（上海）创业投资企业（有限合伙）</t>
+          <t>丰利财富（北京）国际资本管理股份有限公司</t>
         </is>
       </c>
       <c r="E41" t="inlineStr"/>
@@ -3170,7 +3170,7 @@
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -3192,7 +3192,7 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>丰利财富（北京）国际资本管理股份有限公司</t>
+          <t>富海深湾（深圳）移动创新私募创业投资基金合伙企业（有限合伙）</t>
         </is>
       </c>
       <c r="E42" t="inlineStr"/>
@@ -3230,7 +3230,7 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>深圳市创新投资集团有限公司</t>
+          <t>镇江红土创业投资有限公司</t>
         </is>
       </c>
       <c r="E43" t="inlineStr"/>
@@ -3268,7 +3268,7 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>富海深湾（深圳）移动创新私募创业投资基金合伙企业（有限合伙）</t>
+          <t>芜湖富海浩研创业投资基金（有限合伙）</t>
         </is>
       </c>
       <c r="E44" t="inlineStr"/>
@@ -3284,7 +3284,7 @@
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -3306,7 +3306,7 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>昆山红土高新创业投资有限公司</t>
+          <t>东方富海（上海）创业投资企业（有限合伙）</t>
         </is>
       </c>
       <c r="E45" t="inlineStr"/>
@@ -3322,7 +3322,7 @@
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -3344,7 +3344,7 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>镇江红土创业投资有限公司</t>
+          <t>昆山红土高新创业投资有限公司</t>
         </is>
       </c>
       <c r="E46" t="inlineStr"/>
@@ -3420,7 +3420,7 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>芜湖富海浩研创业投资基金（有限合伙）</t>
+          <t>深圳市创新投资集团有限公司</t>
         </is>
       </c>
       <c r="E48" t="inlineStr"/>
@@ -3436,7 +3436,7 @@
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -3458,11 +3458,15 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>富海深湾（深圳）移动创新私募创业投资基金合伙企业（有限合伙）</t>
+          <t>丰利财富（北京）国际资本管理股份有限公司</t>
         </is>
       </c>
       <c r="E49" t="inlineStr"/>
-      <c r="F49" t="inlineStr"/>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>1000.0</t>
+        </is>
+      </c>
       <c r="G49" t="inlineStr"/>
       <c r="H49" t="inlineStr"/>
       <c r="I49" t="inlineStr"/>
@@ -3534,15 +3538,11 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>丰利财富（北京）国际资本管理股份有限公司</t>
+          <t>昆山红土高新创业投资有限公司</t>
         </is>
       </c>
       <c r="E51" t="inlineStr"/>
-      <c r="F51" t="inlineStr">
-        <is>
-          <t>1000.0</t>
-        </is>
-      </c>
+      <c r="F51" t="inlineStr"/>
       <c r="G51" t="inlineStr"/>
       <c r="H51" t="inlineStr"/>
       <c r="I51" t="inlineStr"/>
@@ -3576,7 +3576,7 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>昆山红土高新创业投资有限公司</t>
+          <t>武汉力源信息技术股份有限公司</t>
         </is>
       </c>
       <c r="E52" t="inlineStr"/>
@@ -3592,7 +3592,7 @@
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -3652,7 +3652,7 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>镇江红土创业投资有限公司</t>
+          <t>富海深湾（深圳）移动创新私募创业投资基金合伙企业（有限合伙）</t>
         </is>
       </c>
       <c r="E54" t="inlineStr"/>
@@ -3690,7 +3690,7 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>武汉力源信息技术股份有限公司</t>
+          <t>深圳市创新投资集团有限公司</t>
         </is>
       </c>
       <c r="E55" t="inlineStr"/>
@@ -3706,7 +3706,7 @@
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -3728,7 +3728,7 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>深圳市创新投资集团有限公司</t>
+          <t>镇江红土创业投资有限公司</t>
         </is>
       </c>
       <c r="E56" t="inlineStr"/>
@@ -3766,7 +3766,7 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>刘云锋</t>
+          <t>曾烨</t>
         </is>
       </c>
       <c r="E57" t="inlineStr"/>
@@ -3804,7 +3804,7 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>深圳南山富海中小企业发展基金合伙企业（有限合伙）</t>
+          <t>珠海拓域投资合伙企业（有限合伙）</t>
         </is>
       </c>
       <c r="E58" t="inlineStr"/>
@@ -3842,7 +3842,7 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>曾烨</t>
+          <t>深圳南山富海中小企业发展基金合伙企业（有限合伙）</t>
         </is>
       </c>
       <c r="E59" t="inlineStr"/>
@@ -3858,7 +3858,7 @@
       </c>
       <c r="L59" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -3880,7 +3880,7 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>夏东</t>
+          <t>中科贵银（贵州）创业投资中心（有限合伙）</t>
         </is>
       </c>
       <c r="E60" t="inlineStr"/>
@@ -3918,7 +3918,7 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>中科贵银（贵州）创业投资中心（有限合伙）</t>
+          <t>刘云锋</t>
         </is>
       </c>
       <c r="E61" t="inlineStr"/>
@@ -3934,7 +3934,7 @@
       </c>
       <c r="L61" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -3994,7 +3994,7 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>国科瑞华（北京）创业投资合伙企业（有限合伙）</t>
+          <t>夏东</t>
         </is>
       </c>
       <c r="E63" t="inlineStr"/>
@@ -4032,7 +4032,7 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>珠海拓域投资合伙企业（有限合伙）</t>
+          <t>武汉力源信息技术股份有限公司</t>
         </is>
       </c>
       <c r="E64" t="inlineStr"/>
@@ -4048,7 +4048,7 @@
       </c>
       <c r="L64" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -4070,7 +4070,7 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>武汉力源信息技术股份有限公司</t>
+          <t>国科瑞华（北京）创业投资合伙企业（有限合伙）</t>
         </is>
       </c>
       <c r="E65" t="inlineStr"/>
@@ -4086,7 +4086,7 @@
       </c>
       <c r="L65" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -4108,11 +4108,15 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>火炬电子科技股份有限公司</t>
+          <t>CASREV FUND</t>
         </is>
       </c>
       <c r="E66" t="inlineStr"/>
-      <c r="F66" t="inlineStr"/>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>1800.0</t>
+        </is>
+      </c>
       <c r="G66" t="inlineStr"/>
       <c r="H66" t="inlineStr"/>
       <c r="I66" t="inlineStr"/>
@@ -4124,7 +4128,7 @@
       </c>
       <c r="L66" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -4146,13 +4150,13 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>CASREV FUND</t>
+          <t>国科瑞华（北京）创业投资合伙企业（有限合伙）</t>
         </is>
       </c>
       <c r="E67" t="inlineStr"/>
       <c r="F67" t="inlineStr">
         <is>
-          <t>1800.0</t>
+          <t>7412.0</t>
         </is>
       </c>
       <c r="G67" t="inlineStr"/>
@@ -4188,13 +4192,13 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>深圳南山富海中小企业发展基金合伙企业（有限合伙）</t>
+          <t>夏东</t>
         </is>
       </c>
       <c r="E68" t="inlineStr"/>
       <c r="F68" t="inlineStr">
         <is>
-          <t>3000.0</t>
+          <t>204.0</t>
         </is>
       </c>
       <c r="G68" t="inlineStr"/>
@@ -4230,13 +4234,13 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>国科瑞华（北京）创业投资合伙企业（有限合伙）</t>
+          <t>深圳南山富海中小企业发展基金合伙企业（有限合伙）</t>
         </is>
       </c>
       <c r="E69" t="inlineStr"/>
       <c r="F69" t="inlineStr">
         <is>
-          <t>7412.0</t>
+          <t>3000.0</t>
         </is>
       </c>
       <c r="G69" t="inlineStr"/>
@@ -4314,15 +4318,11 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>夏东</t>
+          <t>火炬电子科技股份有限公司</t>
         </is>
       </c>
       <c r="E71" t="inlineStr"/>
-      <c r="F71" t="inlineStr">
-        <is>
-          <t>204.0</t>
-        </is>
-      </c>
+      <c r="F71" t="inlineStr"/>
       <c r="G71" t="inlineStr"/>
       <c r="H71" t="inlineStr"/>
       <c r="I71" t="inlineStr"/>
@@ -4334,7 +4334,7 @@
       </c>
       <c r="L71" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -4398,15 +4398,11 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>火炬电子科技股份有限公司</t>
+          <t>厦门西堤股权投资合伙企业（有限合伙）</t>
         </is>
       </c>
       <c r="E73" t="inlineStr"/>
-      <c r="F73" t="inlineStr">
-        <is>
-          <t>5000.0</t>
-        </is>
-      </c>
+      <c r="F73" t="inlineStr"/>
       <c r="G73" t="inlineStr"/>
       <c r="H73" t="inlineStr"/>
       <c r="I73" t="inlineStr"/>
@@ -4418,7 +4414,7 @@
       </c>
       <c r="L73" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -4440,11 +4436,15 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>厦门西堤股权投资合伙企业（有限合伙）</t>
+          <t>火炬电子科技股份有限公司</t>
         </is>
       </c>
       <c r="E74" t="inlineStr"/>
-      <c r="F74" t="inlineStr"/>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>5000.0</t>
+        </is>
+      </c>
       <c r="G74" t="inlineStr"/>
       <c r="H74" t="inlineStr"/>
       <c r="I74" t="inlineStr"/>
@@ -4456,7 +4456,7 @@
       </c>
       <c r="L74" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -4516,7 +4516,7 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>周斌</t>
+          <t>黄山供销集团有限公司</t>
         </is>
       </c>
       <c r="E76" t="inlineStr"/>
@@ -4554,11 +4554,15 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>张俊武</t>
+          <t>昆山谷捷金属制品有限公司</t>
         </is>
       </c>
       <c r="E77" t="inlineStr"/>
-      <c r="F77" t="inlineStr"/>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>1000.0</t>
+        </is>
+      </c>
       <c r="G77" t="inlineStr"/>
       <c r="H77" t="inlineStr"/>
       <c r="I77" t="inlineStr"/>
@@ -4570,7 +4574,7 @@
       </c>
       <c r="L77" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -4592,7 +4596,7 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>黄山供销集团有限公司</t>
+          <t>周斌</t>
         </is>
       </c>
       <c r="E78" t="inlineStr"/>
@@ -4630,15 +4634,11 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>昆山谷捷金属制品有限公司</t>
+          <t>张俊武</t>
         </is>
       </c>
       <c r="E79" t="inlineStr"/>
-      <c r="F79" t="inlineStr">
-        <is>
-          <t>1000.0</t>
-        </is>
-      </c>
+      <c r="F79" t="inlineStr"/>
       <c r="G79" t="inlineStr"/>
       <c r="H79" t="inlineStr"/>
       <c r="I79" t="inlineStr"/>
@@ -4650,7 +4650,7 @@
       </c>
       <c r="L79" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -4672,7 +4672,7 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>周斌</t>
+          <t>黄山供销集团有限公司</t>
         </is>
       </c>
       <c r="E80" t="inlineStr"/>
@@ -4706,7 +4706,7 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>张俊武</t>
+          <t>周斌</t>
         </is>
       </c>
       <c r="E81" t="inlineStr"/>
@@ -4740,7 +4740,7 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>黄山供销集团有限公司</t>
+          <t>张俊武</t>
         </is>
       </c>
       <c r="E82" t="inlineStr"/>
@@ -4774,7 +4774,7 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>周斌</t>
+          <t>黄山供销集团有限公司</t>
         </is>
       </c>
       <c r="E83" t="inlineStr"/>
@@ -4812,7 +4812,7 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>张俊武</t>
+          <t>SAIC TECHNOLOGIES FUND II, LLC</t>
         </is>
       </c>
       <c r="E84" t="inlineStr"/>
@@ -4828,7 +4828,7 @@
       </c>
       <c r="L84" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -4850,7 +4850,7 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>SAIC TECHNOLOGIES FUND II, LLC</t>
+          <t>周斌</t>
         </is>
       </c>
       <c r="E85" t="inlineStr"/>
@@ -4866,7 +4866,7 @@
       </c>
       <c r="L85" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -4926,7 +4926,7 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>黄山供销集团有限公司</t>
+          <t>张俊武</t>
         </is>
       </c>
       <c r="E87" t="inlineStr"/>
@@ -5006,11 +5006,15 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>黄山佳捷股权管理中心（有限合伙）</t>
+          <t>上海广弘实业有限公司</t>
         </is>
       </c>
       <c r="E89" t="inlineStr"/>
-      <c r="F89" t="inlineStr"/>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>10377.0</t>
+        </is>
+      </c>
       <c r="G89" t="inlineStr"/>
       <c r="H89" t="inlineStr"/>
       <c r="I89" t="inlineStr"/>
@@ -5022,7 +5026,7 @@
       </c>
       <c r="L89" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -5044,15 +5048,11 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>上海广弘实业有限公司</t>
+          <t>黄山佳捷股权管理中心（有限合伙）</t>
         </is>
       </c>
       <c r="E90" t="inlineStr"/>
-      <c r="F90" t="inlineStr">
-        <is>
-          <t>10377.0</t>
-        </is>
-      </c>
+      <c r="F90" t="inlineStr"/>
       <c r="G90" t="inlineStr"/>
       <c r="H90" t="inlineStr"/>
       <c r="I90" t="inlineStr"/>
@@ -5064,7 +5064,7 @@
       </c>
       <c r="L90" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -5086,7 +5086,7 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>周斌</t>
+          <t>黄山供销集团有限公司</t>
         </is>
       </c>
       <c r="E91" t="inlineStr"/>
@@ -5124,7 +5124,7 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>张俊武</t>
+          <t>SAIC TECHNOLOGIES FUND II, LLC</t>
         </is>
       </c>
       <c r="E92" t="inlineStr"/>
@@ -5162,7 +5162,7 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>SAIC TECHNOLOGIES FUND II, LLC</t>
+          <t>周斌</t>
         </is>
       </c>
       <c r="E93" t="inlineStr"/>
@@ -5200,15 +5200,11 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>黄山佳捷股权管理中心（有限合伙）</t>
+          <t>上海广弘实业有限公司</t>
         </is>
       </c>
       <c r="E94" t="inlineStr"/>
-      <c r="F94" t="inlineStr">
-        <is>
-          <t>2124.81</t>
-        </is>
-      </c>
+      <c r="F94" t="inlineStr"/>
       <c r="G94" t="inlineStr"/>
       <c r="H94" t="inlineStr"/>
       <c r="I94" t="inlineStr"/>
@@ -5218,7 +5214,11 @@
           <t>PASS</t>
         </is>
       </c>
-      <c r="L94" t="inlineStr"/>
+      <c r="L94" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -5238,11 +5238,15 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>上海广弘实业有限公司</t>
+          <t>黄山佳捷股权管理中心（有限合伙）</t>
         </is>
       </c>
       <c r="E95" t="inlineStr"/>
-      <c r="F95" t="inlineStr"/>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>2124.81</t>
+        </is>
+      </c>
       <c r="G95" t="inlineStr"/>
       <c r="H95" t="inlineStr"/>
       <c r="I95" t="inlineStr"/>
@@ -5252,11 +5256,7 @@
           <t>PASS</t>
         </is>
       </c>
-      <c r="L95" t="inlineStr">
-        <is>
-          <t>新增</t>
-        </is>
-      </c>
+      <c r="L95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -5276,7 +5276,7 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>黄山供销集团有限公司</t>
+          <t>张俊武</t>
         </is>
       </c>
       <c r="E96" t="inlineStr"/>
@@ -5964,22 +5964,14 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>上海泽升贸易有限公司</t>
+          <t>友升太平洋(美国)投资有限公司</t>
         </is>
       </c>
       <c r="E110" t="inlineStr"/>
       <c r="F110" t="inlineStr"/>
-      <c r="G110" t="inlineStr">
-        <is>
-          <t>8976.0</t>
-        </is>
-      </c>
+      <c r="G110" t="inlineStr"/>
       <c r="H110" t="inlineStr"/>
-      <c r="I110" t="inlineStr">
-        <is>
-          <t>8976.0</t>
-        </is>
-      </c>
+      <c r="I110" t="inlineStr"/>
       <c r="J110" t="inlineStr"/>
       <c r="K110" t="inlineStr">
         <is>
@@ -5988,7 +5980,7 @@
       </c>
       <c r="L110" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -6010,20 +6002,20 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>深圳市达晨创联私募股权投资基金合伙企业(有限合伙)</t>
+          <t>罗世兵</t>
         </is>
       </c>
       <c r="E111" t="inlineStr"/>
       <c r="F111" t="inlineStr"/>
       <c r="G111" t="inlineStr">
         <is>
-          <t>1800.0</t>
+          <t>204.0</t>
         </is>
       </c>
       <c r="H111" t="inlineStr"/>
       <c r="I111" t="inlineStr">
         <is>
-          <t>1800.0</t>
+          <t>204.0</t>
         </is>
       </c>
       <c r="J111" t="inlineStr"/>
@@ -6056,14 +6048,22 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>上海市青浦县徐泾乡工业公司</t>
+          <t>深圳市达晨创联私募股权投资基金合伙企业(有限合伙)</t>
         </is>
       </c>
       <c r="E112" t="inlineStr"/>
       <c r="F112" t="inlineStr"/>
-      <c r="G112" t="inlineStr"/>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>1800.0</t>
+        </is>
+      </c>
       <c r="H112" t="inlineStr"/>
-      <c r="I112" t="inlineStr"/>
+      <c r="I112" t="inlineStr">
+        <is>
+          <t>1800.0</t>
+        </is>
+      </c>
       <c r="J112" t="inlineStr"/>
       <c r="K112" t="inlineStr">
         <is>
@@ -6072,7 +6072,7 @@
       </c>
       <c r="L112" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -6094,20 +6094,20 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>罗世兵</t>
+          <t>上海泽升贸易有限公司</t>
         </is>
       </c>
       <c r="E113" t="inlineStr"/>
       <c r="F113" t="inlineStr"/>
       <c r="G113" t="inlineStr">
         <is>
-          <t>204.0</t>
+          <t>8976.0</t>
         </is>
       </c>
       <c r="H113" t="inlineStr"/>
       <c r="I113" t="inlineStr">
         <is>
-          <t>204.0</t>
+          <t>8976.0</t>
         </is>
       </c>
       <c r="J113" t="inlineStr"/>
@@ -6140,14 +6140,22 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>友升太平洋(美国)投资有限公司</t>
+          <t>共青城泽升投资管理合伙企业(有限合伙)</t>
         </is>
       </c>
       <c r="E114" t="inlineStr"/>
       <c r="F114" t="inlineStr"/>
-      <c r="G114" t="inlineStr"/>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>1020.0</t>
+        </is>
+      </c>
       <c r="H114" t="inlineStr"/>
-      <c r="I114" t="inlineStr"/>
+      <c r="I114" t="inlineStr">
+        <is>
+          <t>1020.0</t>
+        </is>
+      </c>
       <c r="J114" t="inlineStr"/>
       <c r="K114" t="inlineStr">
         <is>
@@ -6156,7 +6164,7 @@
       </c>
       <c r="L114" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -6178,22 +6186,14 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>共青城泽升投资管理合伙企业(有限合伙)</t>
+          <t>上海市青浦县徐泾乡工业公司</t>
         </is>
       </c>
       <c r="E115" t="inlineStr"/>
       <c r="F115" t="inlineStr"/>
-      <c r="G115" t="inlineStr">
-        <is>
-          <t>1020.0</t>
-        </is>
-      </c>
+      <c r="G115" t="inlineStr"/>
       <c r="H115" t="inlineStr"/>
-      <c r="I115" t="inlineStr">
-        <is>
-          <t>1020.0</t>
-        </is>
-      </c>
+      <c r="I115" t="inlineStr"/>
       <c r="J115" t="inlineStr"/>
       <c r="K115" t="inlineStr">
         <is>
@@ -6202,7 +6202,7 @@
       </c>
       <c r="L115" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -6224,26 +6224,22 @@
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>上海泽升贸易有限公司</t>
-        </is>
-      </c>
-      <c r="E116" t="inlineStr">
-        <is>
-          <t>8976.0</t>
-        </is>
-      </c>
+          <t>上海金浦临港智能科技股权投资基金合伙企业(有限合伙)</t>
+        </is>
+      </c>
+      <c r="E116" t="inlineStr"/>
       <c r="F116" t="inlineStr"/>
       <c r="G116" t="inlineStr">
         <is>
-          <t>8976.0</t>
-        </is>
-      </c>
-      <c r="H116" t="inlineStr">
-        <is>
-          <t>17952.0</t>
-        </is>
-      </c>
-      <c r="I116" t="inlineStr"/>
+          <t>840.0</t>
+        </is>
+      </c>
+      <c r="H116" t="inlineStr"/>
+      <c r="I116" t="inlineStr">
+        <is>
+          <t>840.0</t>
+        </is>
+      </c>
       <c r="J116" t="inlineStr"/>
       <c r="K116" t="inlineStr">
         <is>
@@ -6252,7 +6248,7 @@
       </c>
       <c r="L116" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -6274,22 +6270,26 @@
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>上海金浦科技创业股权投资基金合伙企业(有限合伙)</t>
-        </is>
-      </c>
-      <c r="E117" t="inlineStr"/>
+          <t>罗世兵</t>
+        </is>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>204.0</t>
+        </is>
+      </c>
       <c r="F117" t="inlineStr"/>
       <c r="G117" t="inlineStr">
         <is>
-          <t>360.0</t>
-        </is>
-      </c>
-      <c r="H117" t="inlineStr"/>
-      <c r="I117" t="inlineStr">
-        <is>
-          <t>360.0</t>
-        </is>
-      </c>
+          <t>204.0</t>
+        </is>
+      </c>
+      <c r="H117" t="inlineStr">
+        <is>
+          <t>408.0</t>
+        </is>
+      </c>
+      <c r="I117" t="inlineStr"/>
       <c r="J117" t="inlineStr"/>
       <c r="K117" t="inlineStr">
         <is>
@@ -6298,7 +6298,7 @@
       </c>
       <c r="L117" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -6370,22 +6370,26 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>上海金浦临港智能科技股权投资基金合伙企业(有限合伙)</t>
-        </is>
-      </c>
-      <c r="E119" t="inlineStr"/>
+          <t>上海泽升贸易有限公司</t>
+        </is>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>8976.0</t>
+        </is>
+      </c>
       <c r="F119" t="inlineStr"/>
       <c r="G119" t="inlineStr">
         <is>
-          <t>840.0</t>
-        </is>
-      </c>
-      <c r="H119" t="inlineStr"/>
-      <c r="I119" t="inlineStr">
-        <is>
-          <t>840.0</t>
-        </is>
-      </c>
+          <t>8976.0</t>
+        </is>
+      </c>
+      <c r="H119" t="inlineStr">
+        <is>
+          <t>17952.0</t>
+        </is>
+      </c>
+      <c r="I119" t="inlineStr"/>
       <c r="J119" t="inlineStr"/>
       <c r="K119" t="inlineStr">
         <is>
@@ -6394,7 +6398,7 @@
       </c>
       <c r="L119" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -6416,26 +6420,22 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>罗世兵</t>
-        </is>
-      </c>
-      <c r="E120" t="inlineStr">
-        <is>
-          <t>204.0</t>
-        </is>
-      </c>
+          <t>上海骁墨信息技术服务中心(有限合伙)</t>
+        </is>
+      </c>
+      <c r="E120" t="inlineStr"/>
       <c r="F120" t="inlineStr"/>
       <c r="G120" t="inlineStr">
         <is>
-          <t>204.0</t>
-        </is>
-      </c>
-      <c r="H120" t="inlineStr">
-        <is>
-          <t>408.0</t>
-        </is>
-      </c>
-      <c r="I120" t="inlineStr"/>
+          <t>180.0</t>
+        </is>
+      </c>
+      <c r="H120" t="inlineStr"/>
+      <c r="I120" t="inlineStr">
+        <is>
+          <t>180.0</t>
+        </is>
+      </c>
       <c r="J120" t="inlineStr"/>
       <c r="K120" t="inlineStr">
         <is>
@@ -6444,7 +6444,7 @@
       </c>
       <c r="L120" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -6466,22 +6466,26 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>上海骁墨信息技术服务中心(有限合伙)</t>
-        </is>
-      </c>
-      <c r="E121" t="inlineStr"/>
+          <t>共青城泽升投资管理合伙企业(有限合伙)</t>
+        </is>
+      </c>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>1020.0</t>
+        </is>
+      </c>
       <c r="F121" t="inlineStr"/>
       <c r="G121" t="inlineStr">
         <is>
-          <t>180.0</t>
-        </is>
-      </c>
-      <c r="H121" t="inlineStr"/>
-      <c r="I121" t="inlineStr">
-        <is>
-          <t>180.0</t>
-        </is>
-      </c>
+          <t>1020.0</t>
+        </is>
+      </c>
+      <c r="H121" t="inlineStr">
+        <is>
+          <t>2040.0</t>
+        </is>
+      </c>
+      <c r="I121" t="inlineStr"/>
       <c r="J121" t="inlineStr"/>
       <c r="K121" t="inlineStr">
         <is>
@@ -6490,7 +6494,7 @@
       </c>
       <c r="L121" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -6512,26 +6516,22 @@
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>共青城泽升投资管理合伙企业(有限合伙)</t>
-        </is>
-      </c>
-      <c r="E122" t="inlineStr">
-        <is>
-          <t>1020.0</t>
-        </is>
-      </c>
+          <t>上海金浦科技创业股权投资基金合伙企业(有限合伙)</t>
+        </is>
+      </c>
+      <c r="E122" t="inlineStr"/>
       <c r="F122" t="inlineStr"/>
       <c r="G122" t="inlineStr">
         <is>
-          <t>1020.0</t>
-        </is>
-      </c>
-      <c r="H122" t="inlineStr">
-        <is>
-          <t>2040.0</t>
-        </is>
-      </c>
-      <c r="I122" t="inlineStr"/>
+          <t>360.0</t>
+        </is>
+      </c>
+      <c r="H122" t="inlineStr"/>
+      <c r="I122" t="inlineStr">
+        <is>
+          <t>360.0</t>
+        </is>
+      </c>
       <c r="J122" t="inlineStr"/>
       <c r="K122" t="inlineStr">
         <is>
@@ -6540,7 +6540,7 @@
       </c>
       <c r="L122" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -6562,22 +6562,30 @@
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>江西赣江新区财投晨源股权投资中心(有限合伙)</t>
-        </is>
-      </c>
-      <c r="E123" t="inlineStr"/>
-      <c r="F123" t="inlineStr"/>
+          <t>上海金浦临港智能科技股权投资基金合伙企业(有限合伙)</t>
+        </is>
+      </c>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>840.0</t>
+        </is>
+      </c>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t>7000.0</t>
+        </is>
+      </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>89.2</t>
-        </is>
-      </c>
-      <c r="H123" t="inlineStr"/>
-      <c r="I123" t="inlineStr">
-        <is>
-          <t>89.2</t>
-        </is>
-      </c>
+          <t>840.0</t>
+        </is>
+      </c>
+      <c r="H123" t="inlineStr">
+        <is>
+          <t>1680.0</t>
+        </is>
+      </c>
+      <c r="I123" t="inlineStr"/>
       <c r="J123" t="inlineStr"/>
       <c r="K123" t="inlineStr">
         <is>
@@ -6586,7 +6594,7 @@
       </c>
       <c r="L123" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -6608,20 +6616,20 @@
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>上海联炻企业管理中心(有限合伙)</t>
+          <t>深圳市达晨创程私募股权投资基金企业(有限合伙)</t>
         </is>
       </c>
       <c r="E124" t="inlineStr"/>
       <c r="F124" t="inlineStr"/>
       <c r="G124" t="inlineStr">
         <is>
-          <t>297.3333</t>
+          <t>86.5984</t>
         </is>
       </c>
       <c r="H124" t="inlineStr"/>
       <c r="I124" t="inlineStr">
         <is>
-          <t>297.3333</t>
+          <t>86.5984</t>
         </is>
       </c>
       <c r="J124" t="inlineStr"/>
@@ -6654,20 +6662,20 @@
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>深圳市达晨创程私募股权投资基金企业(有限合伙)</t>
+          <t>深圳市达晨财智创业投资管理有限公司</t>
         </is>
       </c>
       <c r="E125" t="inlineStr"/>
       <c r="F125" t="inlineStr"/>
       <c r="G125" t="inlineStr">
         <is>
-          <t>86.5984</t>
+          <t>29.7333</t>
         </is>
       </c>
       <c r="H125" t="inlineStr"/>
       <c r="I125" t="inlineStr">
         <is>
-          <t>86.5984</t>
+          <t>29.7333</t>
         </is>
       </c>
       <c r="J125" t="inlineStr"/>
@@ -6700,22 +6708,30 @@
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>深圳市达晨财智创业投资管理有限公司</t>
-        </is>
-      </c>
-      <c r="E126" t="inlineStr"/>
-      <c r="F126" t="inlineStr"/>
+          <t>上海金浦科技创业股权投资基金合伙企业(有限合伙)</t>
+        </is>
+      </c>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>360.0</t>
+        </is>
+      </c>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t>3000.0</t>
+        </is>
+      </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>29.7333</t>
-        </is>
-      </c>
-      <c r="H126" t="inlineStr"/>
-      <c r="I126" t="inlineStr">
-        <is>
-          <t>29.7333</t>
-        </is>
-      </c>
+          <t>360.0</t>
+        </is>
+      </c>
+      <c r="H126" t="inlineStr">
+        <is>
+          <t>720.0</t>
+        </is>
+      </c>
+      <c r="I126" t="inlineStr"/>
       <c r="J126" t="inlineStr"/>
       <c r="K126" t="inlineStr">
         <is>
@@ -6724,7 +6740,7 @@
       </c>
       <c r="L126" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -6746,20 +6762,20 @@
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>海南三亚达晨财汇私募股权投资基金合伙企业(有限合伙)</t>
+          <t>深圳市财智创赢私募股权投资企业(有限合伙)</t>
         </is>
       </c>
       <c r="E127" t="inlineStr"/>
       <c r="F127" t="inlineStr"/>
       <c r="G127" t="inlineStr">
         <is>
-          <t>29.7333</t>
+          <t>10.1093</t>
         </is>
       </c>
       <c r="H127" t="inlineStr"/>
       <c r="I127" t="inlineStr">
         <is>
-          <t>29.7333</t>
+          <t>10.1093</t>
         </is>
       </c>
       <c r="J127" t="inlineStr"/>
@@ -6792,27 +6808,27 @@
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>上海金浦临港智能科技股权投资基金合伙企业(有限合伙)</t>
+          <t>上海骁墨信息技术服务中心(有限合伙)</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>840.0</t>
+          <t>180.0</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>7000.0</t>
+          <t>1500.0</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>840.0</t>
+          <t>180.0</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>1680.0</t>
+          <t>360.0</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
@@ -6846,20 +6862,20 @@
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>杭州达晨创程股权投资基金合伙企业(有限合伙)</t>
+          <t>深圳市杉晖创业投资合伙企业(有限合伙)</t>
         </is>
       </c>
       <c r="E129" t="inlineStr"/>
       <c r="F129" t="inlineStr"/>
       <c r="G129" t="inlineStr">
         <is>
-          <t>51.959</t>
+          <t>297.3333</t>
         </is>
       </c>
       <c r="H129" t="inlineStr"/>
       <c r="I129" t="inlineStr">
         <is>
-          <t>51.959</t>
+          <t>297.3333</t>
         </is>
       </c>
       <c r="J129" t="inlineStr"/>
@@ -6892,20 +6908,20 @@
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>上海杉创智至创业投资合伙企业(有限合伙)</t>
+          <t>江西赣江新区财投晨源股权投资中心(有限合伙)</t>
         </is>
       </c>
       <c r="E130" t="inlineStr"/>
       <c r="F130" t="inlineStr"/>
       <c r="G130" t="inlineStr">
         <is>
-          <t>59.4667</t>
+          <t>89.2</t>
         </is>
       </c>
       <c r="H130" t="inlineStr"/>
       <c r="I130" t="inlineStr">
         <is>
-          <t>59.4667</t>
+          <t>89.2</t>
         </is>
       </c>
       <c r="J130" t="inlineStr"/>
@@ -6938,20 +6954,20 @@
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>深圳市财智创赢私募股权投资企业(有限合伙)</t>
+          <t>上海联炻企业管理中心(有限合伙)</t>
         </is>
       </c>
       <c r="E131" t="inlineStr"/>
       <c r="F131" t="inlineStr"/>
       <c r="G131" t="inlineStr">
         <is>
-          <t>10.1093</t>
+          <t>297.3333</t>
         </is>
       </c>
       <c r="H131" t="inlineStr"/>
       <c r="I131" t="inlineStr">
         <is>
-          <t>10.1093</t>
+          <t>297.3333</t>
         </is>
       </c>
       <c r="J131" t="inlineStr"/>
@@ -6984,30 +7000,22 @@
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>上海骁墨信息技术服务中心(有限合伙)</t>
-        </is>
-      </c>
-      <c r="E132" t="inlineStr">
-        <is>
-          <t>180.0</t>
-        </is>
-      </c>
-      <c r="F132" t="inlineStr">
-        <is>
-          <t>1500.0</t>
-        </is>
-      </c>
+          <t>上海杉创智至创业投资合伙企业(有限合伙)</t>
+        </is>
+      </c>
+      <c r="E132" t="inlineStr"/>
+      <c r="F132" t="inlineStr"/>
       <c r="G132" t="inlineStr">
         <is>
-          <t>180.0</t>
-        </is>
-      </c>
-      <c r="H132" t="inlineStr">
-        <is>
-          <t>360.0</t>
-        </is>
-      </c>
-      <c r="I132" t="inlineStr"/>
+          <t>59.4667</t>
+        </is>
+      </c>
+      <c r="H132" t="inlineStr"/>
+      <c r="I132" t="inlineStr">
+        <is>
+          <t>59.4667</t>
+        </is>
+      </c>
       <c r="J132" t="inlineStr"/>
       <c r="K132" t="inlineStr">
         <is>
@@ -7016,7 +7024,7 @@
       </c>
       <c r="L132" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -7038,20 +7046,20 @@
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>深圳市杉晖创业投资合伙企业(有限合伙)</t>
+          <t>海南三亚达晨财汇私募股权投资基金合伙企业(有限合伙)</t>
         </is>
       </c>
       <c r="E133" t="inlineStr"/>
       <c r="F133" t="inlineStr"/>
       <c r="G133" t="inlineStr">
         <is>
-          <t>297.3333</t>
+          <t>29.7333</t>
         </is>
       </c>
       <c r="H133" t="inlineStr"/>
       <c r="I133" t="inlineStr">
         <is>
-          <t>297.3333</t>
+          <t>29.7333</t>
         </is>
       </c>
       <c r="J133" t="inlineStr"/>
@@ -7130,30 +7138,22 @@
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>上海金浦科技创业股权投资基金合伙企业(有限合伙)</t>
-        </is>
-      </c>
-      <c r="E135" t="inlineStr">
-        <is>
-          <t>360.0</t>
-        </is>
-      </c>
-      <c r="F135" t="inlineStr">
-        <is>
-          <t>3000.0</t>
-        </is>
-      </c>
+          <t>杭州达晨创程股权投资基金合伙企业(有限合伙)</t>
+        </is>
+      </c>
+      <c r="E135" t="inlineStr"/>
+      <c r="F135" t="inlineStr"/>
       <c r="G135" t="inlineStr">
         <is>
-          <t>360.0</t>
-        </is>
-      </c>
-      <c r="H135" t="inlineStr">
-        <is>
-          <t>720.0</t>
-        </is>
-      </c>
-      <c r="I135" t="inlineStr"/>
+          <t>51.959</t>
+        </is>
+      </c>
+      <c r="H135" t="inlineStr"/>
+      <c r="I135" t="inlineStr">
+        <is>
+          <t>51.959</t>
+        </is>
+      </c>
       <c r="J135" t="inlineStr"/>
       <c r="K135" t="inlineStr">
         <is>
@@ -7162,7 +7162,7 @@
       </c>
       <c r="L135" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -8034,7 +8034,7 @@
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>周乃鼎</t>
+          <t>黄学英</t>
         </is>
       </c>
       <c r="E153" t="inlineStr"/>
@@ -8050,7 +8050,7 @@
       </c>
       <c r="L153" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -8072,7 +8072,7 @@
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>黄学英</t>
+          <t>华泰大健康一号</t>
         </is>
       </c>
       <c r="E154" t="inlineStr"/>
@@ -8110,7 +8110,7 @@
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>周金清</t>
+          <t>复星惟盈</t>
         </is>
       </c>
       <c r="E155" t="inlineStr"/>
@@ -8148,7 +8148,7 @@
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>国寿疌泉</t>
+          <t>陆民</t>
         </is>
       </c>
       <c r="E156" t="inlineStr"/>
@@ -8162,11 +8162,7 @@
           <t>PASS</t>
         </is>
       </c>
-      <c r="L156" t="inlineStr">
-        <is>
-          <t>新增</t>
-        </is>
-      </c>
+      <c r="L156" t="inlineStr"/>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
@@ -8186,7 +8182,7 @@
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>陆民</t>
+          <t>黄学英/刘鸿雁</t>
         </is>
       </c>
       <c r="E157" t="inlineStr"/>
@@ -8200,7 +8196,11 @@
           <t>PASS</t>
         </is>
       </c>
-      <c r="L157" t="inlineStr"/>
+      <c r="L157" t="inlineStr">
+        <is>
+          <t>退出</t>
+        </is>
+      </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
@@ -8220,7 +8220,7 @@
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>Cheer Rise Consultants Limited</t>
+          <t>周乃鼎</t>
         </is>
       </c>
       <c r="E158" t="inlineStr"/>
@@ -8258,7 +8258,7 @@
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>复星惟盈</t>
+          <t>国寿疌泉</t>
         </is>
       </c>
       <c r="E159" t="inlineStr"/>
@@ -8296,7 +8296,7 @@
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>高新同华</t>
+          <t>史建伟</t>
         </is>
       </c>
       <c r="E160" t="inlineStr"/>
@@ -8312,7 +8312,7 @@
       </c>
       <c r="L160" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -8334,7 +8334,7 @@
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>苏州贤达</t>
+          <t>高新同华</t>
         </is>
       </c>
       <c r="E161" t="inlineStr"/>
@@ -8372,7 +8372,7 @@
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>黄学英/刘鸿雁</t>
+          <t>Cheer Rise Consultants Limited</t>
         </is>
       </c>
       <c r="E162" t="inlineStr"/>
@@ -8410,7 +8410,7 @@
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>华泰大健康一号</t>
+          <t>周金清</t>
         </is>
       </c>
       <c r="E163" t="inlineStr"/>
@@ -8448,7 +8448,7 @@
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>史建伟</t>
+          <t>苏州贤达</t>
         </is>
       </c>
       <c r="E164" t="inlineStr"/>
@@ -8464,7 +8464,7 @@
       </c>
       <c r="L164" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -8486,7 +8486,7 @@
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>深圳中证投资有限责任公司</t>
+          <t>EARN ACE LIMITED</t>
         </is>
       </c>
       <c r="E165" t="inlineStr"/>
@@ -8562,7 +8562,7 @@
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>深圳市伊敦传媒投资基金合伙企业（有限合伙）</t>
+          <t>厦门富凯海创投资管理有限责任公司</t>
         </is>
       </c>
       <c r="E167" t="inlineStr"/>
@@ -8600,7 +8600,7 @@
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>香港迅雷有限公司</t>
+          <t>北京岚锋创视网络科技有限公司</t>
         </is>
       </c>
       <c r="E168" t="inlineStr"/>
@@ -8616,7 +8616,7 @@
       </c>
       <c r="L168" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -8676,7 +8676,7 @@
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>厦门富凯海创投资管理有限责任公司</t>
+          <t>金石智娱股权投资（深圳）合伙企业（有限合伙）</t>
         </is>
       </c>
       <c r="E170" t="inlineStr"/>
@@ -8714,7 +8714,7 @@
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>北京岚锋创视网络科技有限公司</t>
+          <t>深圳中证投资有限责任公司</t>
         </is>
       </c>
       <c r="E171" t="inlineStr"/>
@@ -8730,7 +8730,7 @@
       </c>
       <c r="L171" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -8752,7 +8752,7 @@
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>金石智娱股权投资（深圳）合伙企业（有限合伙）</t>
+          <t>深圳市伊敦传媒投资基金合伙企业（有限合伙）</t>
         </is>
       </c>
       <c r="E172" t="inlineStr"/>
@@ -8790,7 +8790,7 @@
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>EARN ACE LIMITED</t>
+          <t>香港迅雷有限公司</t>
         </is>
       </c>
       <c r="E173" t="inlineStr"/>
@@ -8828,15 +8828,11 @@
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>北京岚锋创视网络科技有限公司</t>
+          <t>EARN ACE LIMITED</t>
         </is>
       </c>
       <c r="E174" t="inlineStr"/>
-      <c r="F174" t="inlineStr">
-        <is>
-          <t>1000.0</t>
-        </is>
-      </c>
+      <c r="F174" t="inlineStr"/>
       <c r="G174" t="inlineStr"/>
       <c r="H174" t="inlineStr"/>
       <c r="I174" t="inlineStr"/>
@@ -8846,7 +8842,11 @@
           <t>PASS</t>
         </is>
       </c>
-      <c r="L174" t="inlineStr"/>
+      <c r="L174" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
@@ -8904,11 +8904,15 @@
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>EARN ACE LIMITED</t>
+          <t>北京岚锋创视网络科技有限公司</t>
         </is>
       </c>
       <c r="E176" t="inlineStr"/>
-      <c r="F176" t="inlineStr"/>
+      <c r="F176" t="inlineStr">
+        <is>
+          <t>1000.0</t>
+        </is>
+      </c>
       <c r="G176" t="inlineStr"/>
       <c r="H176" t="inlineStr"/>
       <c r="I176" t="inlineStr"/>
@@ -8918,11 +8922,7 @@
           <t>PASS</t>
         </is>
       </c>
-      <c r="L176" t="inlineStr">
-        <is>
-          <t>新增</t>
-        </is>
-      </c>
+      <c r="L176" t="inlineStr"/>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
@@ -9018,7 +9018,7 @@
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>北京岚锋创视网络科技有限公司</t>
+          <t>EARN ACE LIMITED</t>
         </is>
       </c>
       <c r="E179" t="inlineStr"/>
@@ -9094,7 +9094,7 @@
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>EARN ACE LIMITED</t>
+          <t>北京岚锋创视网络科技有限公司</t>
         </is>
       </c>
       <c r="E181" t="inlineStr"/>
@@ -9220,7 +9220,7 @@
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>朱绶青</t>
+          <t>深圳市稳正景明创业投资企业(有限合伙)</t>
         </is>
       </c>
       <c r="E184" t="inlineStr"/>
@@ -9236,7 +9236,7 @@
       </c>
       <c r="L184" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -9296,7 +9296,7 @@
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>深圳市稳正景明创业投资企业(有限合伙)</t>
+          <t>朱绶青</t>
         </is>
       </c>
       <c r="E186" t="inlineStr"/>
@@ -9312,7 +9312,7 @@
       </c>
       <c r="L186" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -9334,13 +9334,13 @@
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>四方股份</t>
+          <t>牛威(罗永红代持)</t>
         </is>
       </c>
       <c r="E187" t="inlineStr"/>
       <c r="F187" t="inlineStr">
         <is>
-          <t>1200.0</t>
+          <t>400.0</t>
         </is>
       </c>
       <c r="G187" t="inlineStr"/>
@@ -9494,13 +9494,13 @@
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>牛威(罗永红代持)</t>
+          <t>四方股份</t>
         </is>
       </c>
       <c r="E191" t="inlineStr"/>
       <c r="F191" t="inlineStr">
         <is>
-          <t>400.0</t>
+          <t>1200.0</t>
         </is>
       </c>
       <c r="G191" t="inlineStr"/>
@@ -9536,18 +9536,22 @@
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>牛威</t>
+          <t>策星九天</t>
         </is>
       </c>
       <c r="E192" t="inlineStr"/>
-      <c r="F192" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="G192" t="inlineStr"/>
+      <c r="F192" t="inlineStr"/>
+      <c r="G192" t="inlineStr">
+        <is>
+          <t>2345.0781</t>
+        </is>
+      </c>
       <c r="H192" t="inlineStr"/>
-      <c r="I192" t="inlineStr"/>
+      <c r="I192" t="inlineStr">
+        <is>
+          <t>2345.0781</t>
+        </is>
+      </c>
       <c r="J192" t="inlineStr"/>
       <c r="K192" t="inlineStr">
         <is>
@@ -9556,7 +9560,7 @@
       </c>
       <c r="L192" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -9578,22 +9582,18 @@
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>策星揽月</t>
+          <t>牛威</t>
         </is>
       </c>
       <c r="E193" t="inlineStr"/>
-      <c r="F193" t="inlineStr"/>
-      <c r="G193" t="inlineStr">
-        <is>
-          <t>412.5</t>
-        </is>
-      </c>
+      <c r="F193" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="G193" t="inlineStr"/>
       <c r="H193" t="inlineStr"/>
-      <c r="I193" t="inlineStr">
-        <is>
-          <t>412.5</t>
-        </is>
-      </c>
+      <c r="I193" t="inlineStr"/>
       <c r="J193" t="inlineStr"/>
       <c r="K193" t="inlineStr">
         <is>
@@ -9602,7 +9602,7 @@
       </c>
       <c r="L193" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -9624,20 +9624,20 @@
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>策星九天</t>
+          <t>幸福一期</t>
         </is>
       </c>
       <c r="E194" t="inlineStr"/>
       <c r="F194" t="inlineStr"/>
       <c r="G194" t="inlineStr">
         <is>
-          <t>2345.0781</t>
+          <t>917.4219</t>
         </is>
       </c>
       <c r="H194" t="inlineStr"/>
       <c r="I194" t="inlineStr">
         <is>
-          <t>2345.0781</t>
+          <t>917.4219</t>
         </is>
       </c>
       <c r="J194" t="inlineStr"/>
@@ -9670,20 +9670,20 @@
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>幸福二期</t>
+          <t>策星逐日</t>
         </is>
       </c>
       <c r="E195" t="inlineStr"/>
       <c r="F195" t="inlineStr"/>
       <c r="G195" t="inlineStr">
         <is>
-          <t>300.0</t>
+          <t>171.0</t>
         </is>
       </c>
       <c r="H195" t="inlineStr"/>
       <c r="I195" t="inlineStr">
         <is>
-          <t>300.0</t>
+          <t>171.0</t>
         </is>
       </c>
       <c r="J195" t="inlineStr"/>
@@ -9716,20 +9716,20 @@
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>幸福一期</t>
+          <t>策星银河</t>
         </is>
       </c>
       <c r="E196" t="inlineStr"/>
       <c r="F196" t="inlineStr"/>
       <c r="G196" t="inlineStr">
         <is>
-          <t>917.4219</t>
+          <t>279.0</t>
         </is>
       </c>
       <c r="H196" t="inlineStr"/>
       <c r="I196" t="inlineStr">
         <is>
-          <t>917.4219</t>
+          <t>279.0</t>
         </is>
       </c>
       <c r="J196" t="inlineStr"/>
@@ -9808,20 +9808,20 @@
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>策星逐日</t>
+          <t>幸福二期</t>
         </is>
       </c>
       <c r="E198" t="inlineStr"/>
       <c r="F198" t="inlineStr"/>
       <c r="G198" t="inlineStr">
         <is>
-          <t>171.0</t>
+          <t>300.0</t>
         </is>
       </c>
       <c r="H198" t="inlineStr"/>
       <c r="I198" t="inlineStr">
         <is>
-          <t>171.0</t>
+          <t>300.0</t>
         </is>
       </c>
       <c r="J198" t="inlineStr"/>
@@ -9854,18 +9854,22 @@
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>吴功友</t>
+          <t>策星揽月</t>
         </is>
       </c>
       <c r="E199" t="inlineStr"/>
-      <c r="F199" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="G199" t="inlineStr"/>
+      <c r="F199" t="inlineStr"/>
+      <c r="G199" t="inlineStr">
+        <is>
+          <t>412.5</t>
+        </is>
+      </c>
       <c r="H199" t="inlineStr"/>
-      <c r="I199" t="inlineStr"/>
+      <c r="I199" t="inlineStr">
+        <is>
+          <t>412.5</t>
+        </is>
+      </c>
       <c r="J199" t="inlineStr"/>
       <c r="K199" t="inlineStr">
         <is>
@@ -9874,7 +9878,7 @@
       </c>
       <c r="L199" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -9896,22 +9900,18 @@
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>策星银河</t>
+          <t>吴功友</t>
         </is>
       </c>
       <c r="E200" t="inlineStr"/>
-      <c r="F200" t="inlineStr"/>
-      <c r="G200" t="inlineStr">
-        <is>
-          <t>279.0</t>
-        </is>
-      </c>
+      <c r="F200" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="G200" t="inlineStr"/>
       <c r="H200" t="inlineStr"/>
-      <c r="I200" t="inlineStr">
-        <is>
-          <t>279.0</t>
-        </is>
-      </c>
+      <c r="I200" t="inlineStr"/>
       <c r="J200" t="inlineStr"/>
       <c r="K200" t="inlineStr">
         <is>
@@ -9920,7 +9920,7 @@
       </c>
       <c r="L200" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -10291,7 +10291,7 @@
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>生成时间: 2026-06-12T15:16:11.049655</t>
+          <t>生成时间: 2026-06-12T16:09:12.719780</t>
         </is>
       </c>
     </row>

--- a/outputs/week2_excel/688758_赛分科技_三表抽取.xlsx
+++ b/outputs/week2_excel/688758_赛分科技_三表抽取.xlsx
@@ -2956,11 +2956,15 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>武汉力源信息技术股份有限公司</t>
+          <t>深圳市云汉电子有限公司</t>
         </is>
       </c>
       <c r="E36" t="inlineStr"/>
-      <c r="F36" t="inlineStr"/>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>25.0</t>
+        </is>
+      </c>
       <c r="G36" t="inlineStr"/>
       <c r="H36" t="inlineStr"/>
       <c r="I36" t="inlineStr"/>
@@ -2972,7 +2976,7 @@
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -3032,15 +3036,11 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>刘云锋</t>
+          <t>芜湖富海浩研创业投资基金（有限合伙）</t>
         </is>
       </c>
       <c r="E38" t="inlineStr"/>
-      <c r="F38" t="inlineStr">
-        <is>
-          <t>25.0</t>
-        </is>
-      </c>
+      <c r="F38" t="inlineStr"/>
       <c r="G38" t="inlineStr"/>
       <c r="H38" t="inlineStr"/>
       <c r="I38" t="inlineStr"/>
@@ -3052,7 +3052,7 @@
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -3074,7 +3074,7 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>芜湖富海浩研创业投资基金（有限合伙）</t>
+          <t>武汉力源信息技术股份有限公司</t>
         </is>
       </c>
       <c r="E39" t="inlineStr"/>
@@ -3112,7 +3112,7 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>深圳市云汉电子有限公司</t>
+          <t>刘云锋</t>
         </is>
       </c>
       <c r="E40" t="inlineStr"/>
@@ -3154,7 +3154,7 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>东方富海（上海）创业投资企业（有限合伙）</t>
+          <t>深圳市创新投资集团有限公司</t>
         </is>
       </c>
       <c r="E41" t="inlineStr"/>
@@ -3170,7 +3170,7 @@
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -3192,7 +3192,7 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>深圳市创新投资集团有限公司</t>
+          <t>东方富海（上海）创业投资企业（有限合伙）</t>
         </is>
       </c>
       <c r="E42" t="inlineStr"/>
@@ -3208,7 +3208,7 @@
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -3230,7 +3230,7 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>芜湖富海浩研创业投资基金（有限合伙）</t>
+          <t>富海深湾（深圳）移动创新私募创业投资基金合伙企业（有限合伙）</t>
         </is>
       </c>
       <c r="E43" t="inlineStr"/>
@@ -3246,7 +3246,7 @@
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -3268,7 +3268,7 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>镇江红土创业投资有限公司</t>
+          <t>昆山红土高新创业投资有限公司</t>
         </is>
       </c>
       <c r="E44" t="inlineStr"/>
@@ -3306,7 +3306,7 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>富海深湾（深圳）移动创新私募创业投资基金合伙企业（有限合伙）</t>
+          <t>芜湖富海浩研创业投资基金（有限合伙）</t>
         </is>
       </c>
       <c r="E45" t="inlineStr"/>
@@ -3322,7 +3322,7 @@
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -3344,7 +3344,7 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>丰利财富（北京）国际资本管理股份有限公司</t>
+          <t>武汉力源信息技术股份有限公司</t>
         </is>
       </c>
       <c r="E46" t="inlineStr"/>
@@ -3360,7 +3360,7 @@
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -3382,7 +3382,7 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>武汉力源信息技术股份有限公司</t>
+          <t>镇江红土创业投资有限公司</t>
         </is>
       </c>
       <c r="E47" t="inlineStr"/>
@@ -3398,7 +3398,7 @@
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -3420,7 +3420,7 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>昆山红土高新创业投资有限公司</t>
+          <t>丰利财富（北京）国际资本管理股份有限公司</t>
         </is>
       </c>
       <c r="E48" t="inlineStr"/>
@@ -3458,7 +3458,7 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>武汉力源信息技术股份有限公司</t>
+          <t>深圳市创新投资集团有限公司</t>
         </is>
       </c>
       <c r="E49" t="inlineStr"/>
@@ -3474,7 +3474,7 @@
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -3534,11 +3534,15 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>深圳市创新投资集团有限公司</t>
+          <t>丰利财富（北京）国际资本管理股份有限公司</t>
         </is>
       </c>
       <c r="E51" t="inlineStr"/>
-      <c r="F51" t="inlineStr"/>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>1000.0</t>
+        </is>
+      </c>
       <c r="G51" t="inlineStr"/>
       <c r="H51" t="inlineStr"/>
       <c r="I51" t="inlineStr"/>
@@ -3572,7 +3576,7 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>昆山红土高新创业投资有限公司</t>
+          <t>富海深湾（深圳）移动创新私募创业投资基金合伙企业（有限合伙）</t>
         </is>
       </c>
       <c r="E52" t="inlineStr"/>
@@ -3610,15 +3614,11 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>丰利财富（北京）国际资本管理股份有限公司</t>
+          <t>刘云锋</t>
         </is>
       </c>
       <c r="E53" t="inlineStr"/>
-      <c r="F53" t="inlineStr">
-        <is>
-          <t>1000.0</t>
-        </is>
-      </c>
+      <c r="F53" t="inlineStr"/>
       <c r="G53" t="inlineStr"/>
       <c r="H53" t="inlineStr"/>
       <c r="I53" t="inlineStr"/>
@@ -3630,7 +3630,7 @@
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -3652,7 +3652,7 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>刘云锋</t>
+          <t>武汉力源信息技术股份有限公司</t>
         </is>
       </c>
       <c r="E54" t="inlineStr"/>
@@ -3690,7 +3690,7 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>镇江红土创业投资有限公司</t>
+          <t>昆山红土高新创业投资有限公司</t>
         </is>
       </c>
       <c r="E55" t="inlineStr"/>
@@ -3728,7 +3728,7 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>富海深湾（深圳）移动创新私募创业投资基金合伙企业（有限合伙）</t>
+          <t>镇江红土创业投资有限公司</t>
         </is>
       </c>
       <c r="E56" t="inlineStr"/>
@@ -3842,7 +3842,7 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>刘云锋</t>
+          <t>国科瑞华（北京）创业投资合伙企业（有限合伙）</t>
         </is>
       </c>
       <c r="E59" t="inlineStr"/>
@@ -3858,7 +3858,7 @@
       </c>
       <c r="L59" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -3880,7 +3880,7 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>CASREV FUND</t>
+          <t>珠海拓域投资合伙企业（有限合伙）</t>
         </is>
       </c>
       <c r="E60" t="inlineStr"/>
@@ -3918,7 +3918,7 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>深圳南山富海中小企业发展基金合伙企业（有限合伙）</t>
+          <t>刘云锋</t>
         </is>
       </c>
       <c r="E61" t="inlineStr"/>
@@ -3934,7 +3934,7 @@
       </c>
       <c r="L61" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -3956,7 +3956,7 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>国科瑞华（北京）创业投资合伙企业（有限合伙）</t>
+          <t>深圳南山富海中小企业发展基金合伙企业（有限合伙）</t>
         </is>
       </c>
       <c r="E62" t="inlineStr"/>
@@ -3994,7 +3994,7 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>夏东</t>
+          <t>CASREV FUND</t>
         </is>
       </c>
       <c r="E63" t="inlineStr"/>
@@ -4070,7 +4070,7 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>珠海拓域投资合伙企业（有限合伙）</t>
+          <t>夏东</t>
         </is>
       </c>
       <c r="E65" t="inlineStr"/>
@@ -4108,13 +4108,13 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>夏东</t>
+          <t>深圳南山富海中小企业发展基金合伙企业（有限合伙）</t>
         </is>
       </c>
       <c r="E66" t="inlineStr"/>
       <c r="F66" t="inlineStr">
         <is>
-          <t>204.0</t>
+          <t>3000.0</t>
         </is>
       </c>
       <c r="G66" t="inlineStr"/>
@@ -4150,11 +4150,15 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>火炬电子科技股份有限公司</t>
+          <t>CASREV FUND</t>
         </is>
       </c>
       <c r="E67" t="inlineStr"/>
-      <c r="F67" t="inlineStr"/>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>1800.0</t>
+        </is>
+      </c>
       <c r="G67" t="inlineStr"/>
       <c r="H67" t="inlineStr"/>
       <c r="I67" t="inlineStr"/>
@@ -4166,7 +4170,7 @@
       </c>
       <c r="L67" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -4188,13 +4192,13 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>珠海拓域投资合伙企业（有限合伙）</t>
+          <t>中科贵银（贵州）创业投资中心（有限合伙）</t>
         </is>
       </c>
       <c r="E68" t="inlineStr"/>
       <c r="F68" t="inlineStr">
         <is>
-          <t>1000.0</t>
+          <t>1584.0</t>
         </is>
       </c>
       <c r="G68" t="inlineStr"/>
@@ -4230,13 +4234,13 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>中科贵银（贵州）创业投资中心（有限合伙）</t>
+          <t>国科瑞华（北京）创业投资合伙企业（有限合伙）</t>
         </is>
       </c>
       <c r="E69" t="inlineStr"/>
       <c r="F69" t="inlineStr">
         <is>
-          <t>1584.0</t>
+          <t>7412.0</t>
         </is>
       </c>
       <c r="G69" t="inlineStr"/>
@@ -4272,13 +4276,13 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>CASREV FUND</t>
+          <t>珠海拓域投资合伙企业（有限合伙）</t>
         </is>
       </c>
       <c r="E70" t="inlineStr"/>
       <c r="F70" t="inlineStr">
         <is>
-          <t>1800.0</t>
+          <t>1000.0</t>
         </is>
       </c>
       <c r="G70" t="inlineStr"/>
@@ -4314,13 +4318,13 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>深圳南山富海中小企业发展基金合伙企业（有限合伙）</t>
+          <t>夏东</t>
         </is>
       </c>
       <c r="E71" t="inlineStr"/>
       <c r="F71" t="inlineStr">
         <is>
-          <t>3000.0</t>
+          <t>204.0</t>
         </is>
       </c>
       <c r="G71" t="inlineStr"/>
@@ -4356,15 +4360,11 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>国科瑞华（北京）创业投资合伙企业（有限合伙）</t>
+          <t>火炬电子科技股份有限公司</t>
         </is>
       </c>
       <c r="E72" t="inlineStr"/>
-      <c r="F72" t="inlineStr">
-        <is>
-          <t>7412.0</t>
-        </is>
-      </c>
+      <c r="F72" t="inlineStr"/>
       <c r="G72" t="inlineStr"/>
       <c r="H72" t="inlineStr"/>
       <c r="I72" t="inlineStr"/>
@@ -4376,7 +4376,7 @@
       </c>
       <c r="L72" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -4398,7 +4398,7 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>厦门西堤股权投资合伙企业（有限合伙）</t>
+          <t>中小企业发展基金（深圳有限合伙）</t>
         </is>
       </c>
       <c r="E73" t="inlineStr"/>
@@ -4478,7 +4478,7 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>中小企业发展基金（深圳有限合伙）</t>
+          <t>厦门西堤股权投资合伙企业（有限合伙）</t>
         </is>
       </c>
       <c r="E75" t="inlineStr"/>
@@ -4516,7 +4516,7 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>张俊武</t>
+          <t>周斌</t>
         </is>
       </c>
       <c r="E76" t="inlineStr"/>
@@ -4634,7 +4634,7 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>周斌</t>
+          <t>张俊武</t>
         </is>
       </c>
       <c r="E79" t="inlineStr"/>
@@ -4706,7 +4706,7 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>黄山供销集团有限公司</t>
+          <t>周斌</t>
         </is>
       </c>
       <c r="E81" t="inlineStr"/>
@@ -4740,7 +4740,7 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>周斌</t>
+          <t>黄山供销集团有限公司</t>
         </is>
       </c>
       <c r="E82" t="inlineStr"/>
@@ -4774,7 +4774,7 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>张俊武</t>
+          <t>上海广弘实业有限公司</t>
         </is>
       </c>
       <c r="E83" t="inlineStr"/>
@@ -4790,7 +4790,7 @@
       </c>
       <c r="L83" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -4850,7 +4850,7 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>上海广弘实业有限公司</t>
+          <t>张俊武</t>
         </is>
       </c>
       <c r="E85" t="inlineStr"/>
@@ -4866,7 +4866,7 @@
       </c>
       <c r="L85" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -4888,7 +4888,7 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>黄山供销集团有限公司</t>
+          <t>周斌</t>
         </is>
       </c>
       <c r="E86" t="inlineStr"/>
@@ -4926,7 +4926,7 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>周斌</t>
+          <t>黄山供销集团有限公司</t>
         </is>
       </c>
       <c r="E87" t="inlineStr"/>
@@ -4964,15 +4964,11 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>上海广弘实业有限公司</t>
+          <t>黄山佳捷股权管理中心（有限合伙）</t>
         </is>
       </c>
       <c r="E88" t="inlineStr"/>
-      <c r="F88" t="inlineStr">
-        <is>
-          <t>10377.0</t>
-        </is>
-      </c>
+      <c r="F88" t="inlineStr"/>
       <c r="G88" t="inlineStr"/>
       <c r="H88" t="inlineStr"/>
       <c r="I88" t="inlineStr"/>
@@ -4984,7 +4980,7 @@
       </c>
       <c r="L88" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -5006,11 +5002,15 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>黄山佳捷股权管理中心（有限合伙）</t>
+          <t>上海广弘实业有限公司</t>
         </is>
       </c>
       <c r="E89" t="inlineStr"/>
-      <c r="F89" t="inlineStr"/>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>10377.0</t>
+        </is>
+      </c>
       <c r="G89" t="inlineStr"/>
       <c r="H89" t="inlineStr"/>
       <c r="I89" t="inlineStr"/>
@@ -5022,7 +5022,7 @@
       </c>
       <c r="L89" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -5124,7 +5124,7 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>张俊武</t>
+          <t>上海广弘实业有限公司</t>
         </is>
       </c>
       <c r="E92" t="inlineStr"/>
@@ -5200,7 +5200,7 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>上海广弘实业有限公司</t>
+          <t>张俊武</t>
         </is>
       </c>
       <c r="E94" t="inlineStr"/>
@@ -5238,7 +5238,7 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>黄山供销集团有限公司</t>
+          <t>周斌</t>
         </is>
       </c>
       <c r="E95" t="inlineStr"/>
@@ -5276,7 +5276,7 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>周斌</t>
+          <t>黄山供销集团有限公司</t>
         </is>
       </c>
       <c r="E96" t="inlineStr"/>
@@ -5964,14 +5964,22 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>上海市青浦县徐泾乡工业公司</t>
+          <t>深圳市达晨创联私募股权投资基金合伙企业(有限合伙)</t>
         </is>
       </c>
       <c r="E110" t="inlineStr"/>
       <c r="F110" t="inlineStr"/>
-      <c r="G110" t="inlineStr"/>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>1800.0</t>
+        </is>
+      </c>
       <c r="H110" t="inlineStr"/>
-      <c r="I110" t="inlineStr"/>
+      <c r="I110" t="inlineStr">
+        <is>
+          <t>1800.0</t>
+        </is>
+      </c>
       <c r="J110" t="inlineStr"/>
       <c r="K110" t="inlineStr">
         <is>
@@ -5980,7 +5988,7 @@
       </c>
       <c r="L110" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -6002,22 +6010,14 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>深圳市达晨创联私募股权投资基金合伙企业(有限合伙)</t>
+          <t>友升太平洋(美国)投资有限公司</t>
         </is>
       </c>
       <c r="E111" t="inlineStr"/>
       <c r="F111" t="inlineStr"/>
-      <c r="G111" t="inlineStr">
-        <is>
-          <t>1800.0</t>
-        </is>
-      </c>
+      <c r="G111" t="inlineStr"/>
       <c r="H111" t="inlineStr"/>
-      <c r="I111" t="inlineStr">
-        <is>
-          <t>1800.0</t>
-        </is>
-      </c>
+      <c r="I111" t="inlineStr"/>
       <c r="J111" t="inlineStr"/>
       <c r="K111" t="inlineStr">
         <is>
@@ -6026,7 +6026,7 @@
       </c>
       <c r="L111" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -6048,22 +6048,14 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>上海泽升贸易有限公司</t>
+          <t>上海市青浦县徐泾乡工业公司</t>
         </is>
       </c>
       <c r="E112" t="inlineStr"/>
       <c r="F112" t="inlineStr"/>
-      <c r="G112" t="inlineStr">
-        <is>
-          <t>8976.0</t>
-        </is>
-      </c>
+      <c r="G112" t="inlineStr"/>
       <c r="H112" t="inlineStr"/>
-      <c r="I112" t="inlineStr">
-        <is>
-          <t>8976.0</t>
-        </is>
-      </c>
+      <c r="I112" t="inlineStr"/>
       <c r="J112" t="inlineStr"/>
       <c r="K112" t="inlineStr">
         <is>
@@ -6072,7 +6064,7 @@
       </c>
       <c r="L112" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -6094,20 +6086,20 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>共青城泽升投资管理合伙企业(有限合伙)</t>
+          <t>上海泽升贸易有限公司</t>
         </is>
       </c>
       <c r="E113" t="inlineStr"/>
       <c r="F113" t="inlineStr"/>
       <c r="G113" t="inlineStr">
         <is>
-          <t>1020.0</t>
+          <t>8976.0</t>
         </is>
       </c>
       <c r="H113" t="inlineStr"/>
       <c r="I113" t="inlineStr">
         <is>
-          <t>1020.0</t>
+          <t>8976.0</t>
         </is>
       </c>
       <c r="J113" t="inlineStr"/>
@@ -6140,14 +6132,22 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>友升太平洋(美国)投资有限公司</t>
+          <t>共青城泽升投资管理合伙企业(有限合伙)</t>
         </is>
       </c>
       <c r="E114" t="inlineStr"/>
       <c r="F114" t="inlineStr"/>
-      <c r="G114" t="inlineStr"/>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>1020.0</t>
+        </is>
+      </c>
       <c r="H114" t="inlineStr"/>
-      <c r="I114" t="inlineStr"/>
+      <c r="I114" t="inlineStr">
+        <is>
+          <t>1020.0</t>
+        </is>
+      </c>
       <c r="J114" t="inlineStr"/>
       <c r="K114" t="inlineStr">
         <is>
@@ -6156,7 +6156,7 @@
       </c>
       <c r="L114" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -6224,20 +6224,20 @@
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>上海金浦临港智能科技股权投资基金合伙企业(有限合伙)</t>
+          <t>上海骁墨信息技术服务中心(有限合伙)</t>
         </is>
       </c>
       <c r="E116" t="inlineStr"/>
       <c r="F116" t="inlineStr"/>
       <c r="G116" t="inlineStr">
         <is>
-          <t>840.0</t>
+          <t>180.0</t>
         </is>
       </c>
       <c r="H116" t="inlineStr"/>
       <c r="I116" t="inlineStr">
         <is>
-          <t>840.0</t>
+          <t>180.0</t>
         </is>
       </c>
       <c r="J116" t="inlineStr"/>
@@ -6270,22 +6270,26 @@
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>上海金浦科技创业股权投资基金合伙企业(有限合伙)</t>
-        </is>
-      </c>
-      <c r="E117" t="inlineStr"/>
+          <t>深圳市达晨创联私募股权投资基金合伙企业(有限合伙)</t>
+        </is>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>1800.0</t>
+        </is>
+      </c>
       <c r="F117" t="inlineStr"/>
       <c r="G117" t="inlineStr">
         <is>
-          <t>360.0</t>
-        </is>
-      </c>
-      <c r="H117" t="inlineStr"/>
-      <c r="I117" t="inlineStr">
-        <is>
-          <t>360.0</t>
-        </is>
-      </c>
+          <t>1800.0</t>
+        </is>
+      </c>
+      <c r="H117" t="inlineStr">
+        <is>
+          <t>3600.0</t>
+        </is>
+      </c>
+      <c r="I117" t="inlineStr"/>
       <c r="J117" t="inlineStr"/>
       <c r="K117" t="inlineStr">
         <is>
@@ -6294,7 +6298,7 @@
       </c>
       <c r="L117" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -6316,26 +6320,22 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>深圳市达晨创联私募股权投资基金合伙企业(有限合伙)</t>
-        </is>
-      </c>
-      <c r="E118" t="inlineStr">
-        <is>
-          <t>1800.0</t>
-        </is>
-      </c>
+          <t>上海金浦临港智能科技股权投资基金合伙企业(有限合伙)</t>
+        </is>
+      </c>
+      <c r="E118" t="inlineStr"/>
       <c r="F118" t="inlineStr"/>
       <c r="G118" t="inlineStr">
         <is>
-          <t>1800.0</t>
-        </is>
-      </c>
-      <c r="H118" t="inlineStr">
-        <is>
-          <t>3600.0</t>
-        </is>
-      </c>
-      <c r="I118" t="inlineStr"/>
+          <t>840.0</t>
+        </is>
+      </c>
+      <c r="H118" t="inlineStr"/>
+      <c r="I118" t="inlineStr">
+        <is>
+          <t>840.0</t>
+        </is>
+      </c>
       <c r="J118" t="inlineStr"/>
       <c r="K118" t="inlineStr">
         <is>
@@ -6344,7 +6344,7 @@
       </c>
       <c r="L118" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -6366,22 +6366,26 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>上海骁墨信息技术服务中心(有限合伙)</t>
-        </is>
-      </c>
-      <c r="E119" t="inlineStr"/>
+          <t>上海泽升贸易有限公司</t>
+        </is>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>8976.0</t>
+        </is>
+      </c>
       <c r="F119" t="inlineStr"/>
       <c r="G119" t="inlineStr">
         <is>
-          <t>180.0</t>
-        </is>
-      </c>
-      <c r="H119" t="inlineStr"/>
-      <c r="I119" t="inlineStr">
-        <is>
-          <t>180.0</t>
-        </is>
-      </c>
+          <t>8976.0</t>
+        </is>
+      </c>
+      <c r="H119" t="inlineStr">
+        <is>
+          <t>17952.0</t>
+        </is>
+      </c>
+      <c r="I119" t="inlineStr"/>
       <c r="J119" t="inlineStr"/>
       <c r="K119" t="inlineStr">
         <is>
@@ -6390,7 +6394,7 @@
       </c>
       <c r="L119" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -6412,23 +6416,23 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>上海泽升贸易有限公司</t>
+          <t>共青城泽升投资管理合伙企业(有限合伙)</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>8976.0</t>
+          <t>1020.0</t>
         </is>
       </c>
       <c r="F120" t="inlineStr"/>
       <c r="G120" t="inlineStr">
         <is>
-          <t>8976.0</t>
+          <t>1020.0</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>17952.0</t>
+          <t>2040.0</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
@@ -6462,26 +6466,22 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>共青城泽升投资管理合伙企业(有限合伙)</t>
-        </is>
-      </c>
-      <c r="E121" t="inlineStr">
-        <is>
-          <t>1020.0</t>
-        </is>
-      </c>
+          <t>上海金浦科技创业股权投资基金合伙企业(有限合伙)</t>
+        </is>
+      </c>
+      <c r="E121" t="inlineStr"/>
       <c r="F121" t="inlineStr"/>
       <c r="G121" t="inlineStr">
         <is>
-          <t>1020.0</t>
-        </is>
-      </c>
-      <c r="H121" t="inlineStr">
-        <is>
-          <t>2040.0</t>
-        </is>
-      </c>
-      <c r="I121" t="inlineStr"/>
+          <t>360.0</t>
+        </is>
+      </c>
+      <c r="H121" t="inlineStr"/>
+      <c r="I121" t="inlineStr">
+        <is>
+          <t>360.0</t>
+        </is>
+      </c>
       <c r="J121" t="inlineStr"/>
       <c r="K121" t="inlineStr">
         <is>
@@ -6490,7 +6490,7 @@
       </c>
       <c r="L121" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -6562,20 +6562,20 @@
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>深圳市达晨财智创业投资管理有限公司</t>
+          <t>深圳市财智创赢私募股权投资企业(有限合伙)</t>
         </is>
       </c>
       <c r="E123" t="inlineStr"/>
       <c r="F123" t="inlineStr"/>
       <c r="G123" t="inlineStr">
         <is>
-          <t>29.7333</t>
+          <t>10.1093</t>
         </is>
       </c>
       <c r="H123" t="inlineStr"/>
       <c r="I123" t="inlineStr">
         <is>
-          <t>29.7333</t>
+          <t>10.1093</t>
         </is>
       </c>
       <c r="J123" t="inlineStr"/>
@@ -6608,20 +6608,20 @@
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>江西赣江新区财投晨源股权投资中心(有限合伙)</t>
+          <t>深圳市达晨创程私募股权投资基金企业(有限合伙)</t>
         </is>
       </c>
       <c r="E124" t="inlineStr"/>
       <c r="F124" t="inlineStr"/>
       <c r="G124" t="inlineStr">
         <is>
-          <t>89.2</t>
+          <t>86.5984</t>
         </is>
       </c>
       <c r="H124" t="inlineStr"/>
       <c r="I124" t="inlineStr">
         <is>
-          <t>89.2</t>
+          <t>86.5984</t>
         </is>
       </c>
       <c r="J124" t="inlineStr"/>
@@ -6654,20 +6654,20 @@
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>上海联炻企业管理中心(有限合伙)</t>
+          <t>上海杉创智至创业投资合伙企业(有限合伙)</t>
         </is>
       </c>
       <c r="E125" t="inlineStr"/>
       <c r="F125" t="inlineStr"/>
       <c r="G125" t="inlineStr">
         <is>
-          <t>297.3333</t>
+          <t>59.4667</t>
         </is>
       </c>
       <c r="H125" t="inlineStr"/>
       <c r="I125" t="inlineStr">
         <is>
-          <t>297.3333</t>
+          <t>59.4667</t>
         </is>
       </c>
       <c r="J125" t="inlineStr"/>
@@ -6700,20 +6700,20 @@
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>海南三亚达晨财汇私募股权投资基金合伙企业(有限合伙)</t>
+          <t>杭州达晨创程股权投资基金合伙企业(有限合伙)</t>
         </is>
       </c>
       <c r="E126" t="inlineStr"/>
       <c r="F126" t="inlineStr"/>
       <c r="G126" t="inlineStr">
         <is>
-          <t>29.7333</t>
+          <t>51.959</t>
         </is>
       </c>
       <c r="H126" t="inlineStr"/>
       <c r="I126" t="inlineStr">
         <is>
-          <t>29.7333</t>
+          <t>51.959</t>
         </is>
       </c>
       <c r="J126" t="inlineStr"/>
@@ -6746,30 +6746,22 @@
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>上海骁墨信息技术服务中心(有限合伙)</t>
-        </is>
-      </c>
-      <c r="E127" t="inlineStr">
-        <is>
-          <t>180.0</t>
-        </is>
-      </c>
-      <c r="F127" t="inlineStr">
-        <is>
-          <t>1500.0</t>
-        </is>
-      </c>
+          <t>深圳市达晨财智创业投资管理有限公司</t>
+        </is>
+      </c>
+      <c r="E127" t="inlineStr"/>
+      <c r="F127" t="inlineStr"/>
       <c r="G127" t="inlineStr">
         <is>
-          <t>180.0</t>
-        </is>
-      </c>
-      <c r="H127" t="inlineStr">
-        <is>
-          <t>360.0</t>
-        </is>
-      </c>
-      <c r="I127" t="inlineStr"/>
+          <t>29.7333</t>
+        </is>
+      </c>
+      <c r="H127" t="inlineStr"/>
+      <c r="I127" t="inlineStr">
+        <is>
+          <t>29.7333</t>
+        </is>
+      </c>
       <c r="J127" t="inlineStr"/>
       <c r="K127" t="inlineStr">
         <is>
@@ -6778,7 +6770,7 @@
       </c>
       <c r="L127" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -6800,27 +6792,27 @@
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>上海金浦临港智能科技股权投资基金合伙企业(有限合伙)</t>
+          <t>上海金浦科技创业股权投资基金合伙企业(有限合伙)</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>840.0</t>
+          <t>360.0</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>7000.0</t>
+          <t>3000.0</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>840.0</t>
+          <t>360.0</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>1680.0</t>
+          <t>720.0</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
@@ -6854,20 +6846,20 @@
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>安吉璞颉企业管理合伙企业(有限合伙)</t>
+          <t>上海联炻企业管理中心(有限合伙)</t>
         </is>
       </c>
       <c r="E129" t="inlineStr"/>
       <c r="F129" t="inlineStr"/>
       <c r="G129" t="inlineStr">
         <is>
-          <t>148.6667</t>
+          <t>297.3333</t>
         </is>
       </c>
       <c r="H129" t="inlineStr"/>
       <c r="I129" t="inlineStr">
         <is>
-          <t>148.6667</t>
+          <t>297.3333</t>
         </is>
       </c>
       <c r="J129" t="inlineStr"/>
@@ -6900,22 +6892,30 @@
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>上海杉创智至创业投资合伙企业(有限合伙)</t>
-        </is>
-      </c>
-      <c r="E130" t="inlineStr"/>
-      <c r="F130" t="inlineStr"/>
+          <t>上海骁墨信息技术服务中心(有限合伙)</t>
+        </is>
+      </c>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>180.0</t>
+        </is>
+      </c>
+      <c r="F130" t="inlineStr">
+        <is>
+          <t>1500.0</t>
+        </is>
+      </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>59.4667</t>
-        </is>
-      </c>
-      <c r="H130" t="inlineStr"/>
-      <c r="I130" t="inlineStr">
-        <is>
-          <t>59.4667</t>
-        </is>
-      </c>
+          <t>180.0</t>
+        </is>
+      </c>
+      <c r="H130" t="inlineStr">
+        <is>
+          <t>360.0</t>
+        </is>
+      </c>
+      <c r="I130" t="inlineStr"/>
       <c r="J130" t="inlineStr"/>
       <c r="K130" t="inlineStr">
         <is>
@@ -6924,7 +6924,7 @@
       </c>
       <c r="L130" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -6946,20 +6946,20 @@
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>深圳市财智创赢私募股权投资企业(有限合伙)</t>
+          <t>深圳市杉晖创业投资合伙企业(有限合伙)</t>
         </is>
       </c>
       <c r="E131" t="inlineStr"/>
       <c r="F131" t="inlineStr"/>
       <c r="G131" t="inlineStr">
         <is>
-          <t>10.1093</t>
+          <t>297.3333</t>
         </is>
       </c>
       <c r="H131" t="inlineStr"/>
       <c r="I131" t="inlineStr">
         <is>
-          <t>10.1093</t>
+          <t>297.3333</t>
         </is>
       </c>
       <c r="J131" t="inlineStr"/>
@@ -6992,27 +6992,27 @@
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>上海金浦科技创业股权投资基金合伙企业(有限合伙)</t>
+          <t>上海金浦临港智能科技股权投资基金合伙企业(有限合伙)</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>360.0</t>
+          <t>840.0</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>3000.0</t>
+          <t>7000.0</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>360.0</t>
+          <t>840.0</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>720.0</t>
+          <t>1680.0</t>
         </is>
       </c>
       <c r="I132" t="inlineStr"/>
@@ -7046,20 +7046,20 @@
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>深圳市杉晖创业投资合伙企业(有限合伙)</t>
+          <t>安吉璞颉企业管理合伙企业(有限合伙)</t>
         </is>
       </c>
       <c r="E133" t="inlineStr"/>
       <c r="F133" t="inlineStr"/>
       <c r="G133" t="inlineStr">
         <is>
-          <t>297.3333</t>
+          <t>148.6667</t>
         </is>
       </c>
       <c r="H133" t="inlineStr"/>
       <c r="I133" t="inlineStr">
         <is>
-          <t>297.3333</t>
+          <t>148.6667</t>
         </is>
       </c>
       <c r="J133" t="inlineStr"/>
@@ -7092,20 +7092,20 @@
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>深圳市达晨创程私募股权投资基金企业(有限合伙)</t>
+          <t>海南三亚达晨财汇私募股权投资基金合伙企业(有限合伙)</t>
         </is>
       </c>
       <c r="E134" t="inlineStr"/>
       <c r="F134" t="inlineStr"/>
       <c r="G134" t="inlineStr">
         <is>
-          <t>86.5984</t>
+          <t>29.7333</t>
         </is>
       </c>
       <c r="H134" t="inlineStr"/>
       <c r="I134" t="inlineStr">
         <is>
-          <t>86.5984</t>
+          <t>29.7333</t>
         </is>
       </c>
       <c r="J134" t="inlineStr"/>
@@ -7138,20 +7138,20 @@
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>杭州达晨创程股权投资基金合伙企业(有限合伙)</t>
+          <t>江西赣江新区财投晨源股权投资中心(有限合伙)</t>
         </is>
       </c>
       <c r="E135" t="inlineStr"/>
       <c r="F135" t="inlineStr"/>
       <c r="G135" t="inlineStr">
         <is>
-          <t>51.959</t>
+          <t>89.2</t>
         </is>
       </c>
       <c r="H135" t="inlineStr"/>
       <c r="I135" t="inlineStr">
         <is>
-          <t>51.959</t>
+          <t>89.2</t>
         </is>
       </c>
       <c r="J135" t="inlineStr"/>
@@ -8034,7 +8034,7 @@
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>国寿疌泉</t>
+          <t>苏州贤达</t>
         </is>
       </c>
       <c r="E153" t="inlineStr"/>
@@ -8072,7 +8072,7 @@
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>Cheer Rise Consultants Limited</t>
+          <t>史建伟</t>
         </is>
       </c>
       <c r="E154" t="inlineStr"/>
@@ -8110,7 +8110,7 @@
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>复星惟盈</t>
+          <t>黄学英/刘鸿雁</t>
         </is>
       </c>
       <c r="E155" t="inlineStr"/>
@@ -8126,7 +8126,7 @@
       </c>
       <c r="L155" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -8148,7 +8148,7 @@
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>苏州贤达</t>
+          <t>国寿疌泉</t>
         </is>
       </c>
       <c r="E156" t="inlineStr"/>
@@ -8186,7 +8186,7 @@
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>黄学英</t>
+          <t>周乃鼎</t>
         </is>
       </c>
       <c r="E157" t="inlineStr"/>
@@ -8202,7 +8202,7 @@
       </c>
       <c r="L157" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -8224,7 +8224,7 @@
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>史建伟</t>
+          <t>周金清</t>
         </is>
       </c>
       <c r="E158" t="inlineStr"/>
@@ -8240,7 +8240,7 @@
       </c>
       <c r="L158" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -8262,7 +8262,7 @@
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>周金清</t>
+          <t>复星惟盈</t>
         </is>
       </c>
       <c r="E159" t="inlineStr"/>
@@ -8300,7 +8300,7 @@
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>周乃鼎</t>
+          <t>Cheer Rise Consultants Limited</t>
         </is>
       </c>
       <c r="E160" t="inlineStr"/>
@@ -8338,7 +8338,7 @@
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>华泰大健康一号</t>
+          <t>陆民</t>
         </is>
       </c>
       <c r="E161" t="inlineStr"/>
@@ -8352,11 +8352,7 @@
           <t>PASS</t>
         </is>
       </c>
-      <c r="L161" t="inlineStr">
-        <is>
-          <t>新增</t>
-        </is>
-      </c>
+      <c r="L161" t="inlineStr"/>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
@@ -8376,7 +8372,7 @@
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>高新同华</t>
+          <t>黄学英</t>
         </is>
       </c>
       <c r="E162" t="inlineStr"/>
@@ -8414,7 +8410,7 @@
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>陆民</t>
+          <t>华泰大健康一号</t>
         </is>
       </c>
       <c r="E163" t="inlineStr"/>
@@ -8428,7 +8424,11 @@
           <t>PASS</t>
         </is>
       </c>
-      <c r="L163" t="inlineStr"/>
+      <c r="L163" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
@@ -8448,7 +8448,7 @@
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>黄学英/刘鸿雁</t>
+          <t>高新同华</t>
         </is>
       </c>
       <c r="E164" t="inlineStr"/>
@@ -8464,7 +8464,7 @@
       </c>
       <c r="L164" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -8486,7 +8486,7 @@
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>EARN ACE LIMITED</t>
+          <t>厦门富凯海创投资管理有限责任公司</t>
         </is>
       </c>
       <c r="E165" t="inlineStr"/>
@@ -8524,7 +8524,7 @@
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>深圳中证投资有限责任公司</t>
+          <t>QM101 Limited</t>
         </is>
       </c>
       <c r="E166" t="inlineStr"/>
@@ -8562,7 +8562,7 @@
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>华金同达（深圳）投资合伙企业（有限合伙）</t>
+          <t>深圳市伊敦传媒投资基金合伙企业（有限合伙）</t>
         </is>
       </c>
       <c r="E167" t="inlineStr"/>
@@ -8600,7 +8600,7 @@
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>香港迅雷有限公司</t>
+          <t>金石智娱股权投资（深圳）合伙企业（有限合伙）</t>
         </is>
       </c>
       <c r="E168" t="inlineStr"/>
@@ -8638,7 +8638,7 @@
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>北京岚锋创视网络科技有限公司</t>
+          <t>香港迅雷有限公司</t>
         </is>
       </c>
       <c r="E169" t="inlineStr"/>
@@ -8654,7 +8654,7 @@
       </c>
       <c r="L169" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -8676,7 +8676,7 @@
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>深圳市伊敦传媒投资基金合伙企业（有限合伙）</t>
+          <t>北京岚锋创视网络科技有限公司</t>
         </is>
       </c>
       <c r="E170" t="inlineStr"/>
@@ -8692,7 +8692,7 @@
       </c>
       <c r="L170" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -8714,7 +8714,7 @@
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>QM101 Limited</t>
+          <t>EARN ACE LIMITED</t>
         </is>
       </c>
       <c r="E171" t="inlineStr"/>
@@ -8752,7 +8752,7 @@
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>金石智娱股权投资（深圳）合伙企业（有限合伙）</t>
+          <t>华金同达（深圳）投资合伙企业（有限合伙）</t>
         </is>
       </c>
       <c r="E172" t="inlineStr"/>
@@ -8790,7 +8790,7 @@
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>厦门富凯海创投资管理有限责任公司</t>
+          <t>深圳中证投资有限责任公司</t>
         </is>
       </c>
       <c r="E173" t="inlineStr"/>
@@ -8828,7 +8828,7 @@
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>QM101 Limited</t>
+          <t>香港迅雷有限公司</t>
         </is>
       </c>
       <c r="E174" t="inlineStr"/>
@@ -8866,7 +8866,7 @@
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>EARN ACE LIMITED</t>
+          <t>QM101 Limited</t>
         </is>
       </c>
       <c r="E175" t="inlineStr"/>
@@ -8904,7 +8904,7 @@
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>香港迅雷有限公司</t>
+          <t>EARN ACE LIMITED</t>
         </is>
       </c>
       <c r="E176" t="inlineStr"/>
@@ -9018,7 +9018,7 @@
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>QM101 Limited</t>
+          <t>香港迅雷有限公司</t>
         </is>
       </c>
       <c r="E179" t="inlineStr"/>
@@ -9056,7 +9056,7 @@
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>EARN ACE LIMITED</t>
+          <t>QM101 Limited</t>
         </is>
       </c>
       <c r="E180" t="inlineStr"/>
@@ -9094,7 +9094,7 @@
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>香港迅雷有限公司</t>
+          <t>EARN ACE LIMITED</t>
         </is>
       </c>
       <c r="E181" t="inlineStr"/>
@@ -9193,7 +9193,7 @@
       </c>
       <c r="K183" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>待复核</t>
         </is>
       </c>
       <c r="L183" t="inlineStr">
@@ -9220,7 +9220,7 @@
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>盛祎</t>
+          <t>朱绶青</t>
         </is>
       </c>
       <c r="E184" t="inlineStr"/>
@@ -9258,7 +9258,7 @@
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>深圳市稳正景明创业投资企业(有限合伙)</t>
+          <t>盛祎</t>
         </is>
       </c>
       <c r="E185" t="inlineStr"/>
@@ -9274,7 +9274,7 @@
       </c>
       <c r="L185" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -9296,7 +9296,7 @@
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>朱绶青</t>
+          <t>深圳市稳正景明创业投资企业(有限合伙)</t>
         </is>
       </c>
       <c r="E186" t="inlineStr"/>
@@ -9312,7 +9312,7 @@
       </c>
       <c r="L186" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -9334,13 +9334,13 @@
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>四方股份</t>
+          <t>牛威(罗永红代持)</t>
         </is>
       </c>
       <c r="E187" t="inlineStr"/>
       <c r="F187" t="inlineStr">
         <is>
-          <t>1200.0</t>
+          <t>400.0</t>
         </is>
       </c>
       <c r="G187" t="inlineStr"/>
@@ -9376,15 +9376,11 @@
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>吴功友(王金林代持)</t>
+          <t>吴功友</t>
         </is>
       </c>
       <c r="E188" t="inlineStr"/>
-      <c r="F188" t="inlineStr">
-        <is>
-          <t>400.0</t>
-        </is>
-      </c>
+      <c r="F188" t="inlineStr"/>
       <c r="G188" t="inlineStr"/>
       <c r="H188" t="inlineStr"/>
       <c r="I188" t="inlineStr"/>
@@ -9396,7 +9392,7 @@
       </c>
       <c r="L188" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -9456,11 +9452,15 @@
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>吴功友</t>
+          <t>四方股份</t>
         </is>
       </c>
       <c r="E190" t="inlineStr"/>
-      <c r="F190" t="inlineStr"/>
+      <c r="F190" t="inlineStr">
+        <is>
+          <t>1200.0</t>
+        </is>
+      </c>
       <c r="G190" t="inlineStr"/>
       <c r="H190" t="inlineStr"/>
       <c r="I190" t="inlineStr"/>
@@ -9472,7 +9472,7 @@
       </c>
       <c r="L190" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -9494,7 +9494,7 @@
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>牛威(罗永红代持)</t>
+          <t>吴功友(王金林代持)</t>
         </is>
       </c>
       <c r="E191" t="inlineStr"/>
@@ -9536,22 +9536,18 @@
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>策星九天</t>
+          <t>牛威</t>
         </is>
       </c>
       <c r="E192" t="inlineStr"/>
-      <c r="F192" t="inlineStr"/>
-      <c r="G192" t="inlineStr">
-        <is>
-          <t>2345.0781</t>
-        </is>
-      </c>
+      <c r="F192" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="G192" t="inlineStr"/>
       <c r="H192" t="inlineStr"/>
-      <c r="I192" t="inlineStr">
-        <is>
-          <t>2345.0781</t>
-        </is>
-      </c>
+      <c r="I192" t="inlineStr"/>
       <c r="J192" t="inlineStr"/>
       <c r="K192" t="inlineStr">
         <is>
@@ -9560,7 +9556,7 @@
       </c>
       <c r="L192" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -9582,20 +9578,20 @@
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>幸福二期</t>
+          <t>策星揽月</t>
         </is>
       </c>
       <c r="E193" t="inlineStr"/>
       <c r="F193" t="inlineStr"/>
       <c r="G193" t="inlineStr">
         <is>
-          <t>300.0</t>
+          <t>412.5</t>
         </is>
       </c>
       <c r="H193" t="inlineStr"/>
       <c r="I193" t="inlineStr">
         <is>
-          <t>300.0</t>
+          <t>412.5</t>
         </is>
       </c>
       <c r="J193" t="inlineStr"/>
@@ -9628,20 +9624,20 @@
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>策星逐日</t>
+          <t>策星九天</t>
         </is>
       </c>
       <c r="E194" t="inlineStr"/>
       <c r="F194" t="inlineStr"/>
       <c r="G194" t="inlineStr">
         <is>
-          <t>171.0</t>
+          <t>2345.0781</t>
         </is>
       </c>
       <c r="H194" t="inlineStr"/>
       <c r="I194" t="inlineStr">
         <is>
-          <t>171.0</t>
+          <t>2345.0781</t>
         </is>
       </c>
       <c r="J194" t="inlineStr"/>
@@ -9674,18 +9670,22 @@
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>牛威</t>
+          <t>幸福二期</t>
         </is>
       </c>
       <c r="E195" t="inlineStr"/>
-      <c r="F195" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="G195" t="inlineStr"/>
+      <c r="F195" t="inlineStr"/>
+      <c r="G195" t="inlineStr">
+        <is>
+          <t>300.0</t>
+        </is>
+      </c>
       <c r="H195" t="inlineStr"/>
-      <c r="I195" t="inlineStr"/>
+      <c r="I195" t="inlineStr">
+        <is>
+          <t>300.0</t>
+        </is>
+      </c>
       <c r="J195" t="inlineStr"/>
       <c r="K195" t="inlineStr">
         <is>
@@ -9694,7 +9694,7 @@
       </c>
       <c r="L195" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -9716,18 +9716,22 @@
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>吴功友</t>
+          <t>策星银河</t>
         </is>
       </c>
       <c r="E196" t="inlineStr"/>
-      <c r="F196" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="G196" t="inlineStr"/>
+      <c r="F196" t="inlineStr"/>
+      <c r="G196" t="inlineStr">
+        <is>
+          <t>279.0</t>
+        </is>
+      </c>
       <c r="H196" t="inlineStr"/>
-      <c r="I196" t="inlineStr"/>
+      <c r="I196" t="inlineStr">
+        <is>
+          <t>279.0</t>
+        </is>
+      </c>
       <c r="J196" t="inlineStr"/>
       <c r="K196" t="inlineStr">
         <is>
@@ -9736,7 +9740,7 @@
       </c>
       <c r="L196" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -9758,22 +9762,18 @@
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>中科星图股份有限公司</t>
+          <t>吴功友</t>
         </is>
       </c>
       <c r="E197" t="inlineStr"/>
-      <c r="F197" t="inlineStr"/>
-      <c r="G197" t="inlineStr">
-        <is>
-          <t>3825.0</t>
-        </is>
-      </c>
+      <c r="F197" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="G197" t="inlineStr"/>
       <c r="H197" t="inlineStr"/>
-      <c r="I197" t="inlineStr">
-        <is>
-          <t>3825.0</t>
-        </is>
-      </c>
+      <c r="I197" t="inlineStr"/>
       <c r="J197" t="inlineStr"/>
       <c r="K197" t="inlineStr">
         <is>
@@ -9782,7 +9782,7 @@
       </c>
       <c r="L197" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -9804,20 +9804,20 @@
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>幸福一期</t>
+          <t>中科星图股份有限公司</t>
         </is>
       </c>
       <c r="E198" t="inlineStr"/>
       <c r="F198" t="inlineStr"/>
       <c r="G198" t="inlineStr">
         <is>
-          <t>917.4219</t>
+          <t>3825.0</t>
         </is>
       </c>
       <c r="H198" t="inlineStr"/>
       <c r="I198" t="inlineStr">
         <is>
-          <t>917.4219</t>
+          <t>3825.0</t>
         </is>
       </c>
       <c r="J198" t="inlineStr"/>
@@ -9850,20 +9850,20 @@
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>策星揽月</t>
+          <t>幸福一期</t>
         </is>
       </c>
       <c r="E199" t="inlineStr"/>
       <c r="F199" t="inlineStr"/>
       <c r="G199" t="inlineStr">
         <is>
-          <t>412.5</t>
+          <t>917.4219</t>
         </is>
       </c>
       <c r="H199" t="inlineStr"/>
       <c r="I199" t="inlineStr">
         <is>
-          <t>412.5</t>
+          <t>917.4219</t>
         </is>
       </c>
       <c r="J199" t="inlineStr"/>
@@ -9896,20 +9896,20 @@
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>策星银河</t>
+          <t>策星逐日</t>
         </is>
       </c>
       <c r="E200" t="inlineStr"/>
       <c r="F200" t="inlineStr"/>
       <c r="G200" t="inlineStr">
         <is>
-          <t>279.0</t>
+          <t>171.0</t>
         </is>
       </c>
       <c r="H200" t="inlineStr"/>
       <c r="I200" t="inlineStr">
         <is>
-          <t>279.0</t>
+          <t>171.0</t>
         </is>
       </c>
       <c r="J200" t="inlineStr"/>
@@ -10291,7 +10291,7 @@
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>生成时间: 2026-06-12T17:05:42.698594</t>
+          <t>生成时间: 2026-06-12T17:10:43.408884</t>
         </is>
       </c>
     </row>
